--- a/test_plans/CCC_Web_Platform_MTP.xlsx
+++ b/test_plans/CCC_Web_Platform_MTP.xlsx
@@ -4937,7 +4937,11 @@
       </c>
       <c r="E3" s="66" t="n"/>
       <c r="F3" s="73" t="n"/>
-      <c r="G3" s="73" t="n"/>
+      <c r="G3" s="73" t="inlineStr">
+        <is>
+          <t>✅ Automated: test_vv_01_land_and_bulk_approve (Playwright). Passing on stage.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="85" t="inlineStr">
@@ -4968,7 +4972,11 @@
       </c>
       <c r="E4" s="66" t="n"/>
       <c r="F4" s="73" t="n"/>
-      <c r="G4" s="73" t="n"/>
+      <c r="G4" s="73" t="inlineStr">
+        <is>
+          <t>✅ Covered by test_worker_gaps.test_src_w_46_worker_profile_kpis (worker-profile KPI header).</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="85" t="inlineStr">
@@ -4996,7 +5004,11 @@
       </c>
       <c r="E5" s="66" t="n"/>
       <c r="F5" s="73" t="n"/>
-      <c r="G5" s="73" t="n"/>
+      <c r="G5" s="73" t="inlineStr">
+        <is>
+          <t>✅ Automated: test_vv_03_image_carousel. Skips on covid_opp_test - blocked by user_visit_details 500 (opp missing OpportunityVerificationFlags); needs an opp whose details panel renders.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="85" t="inlineStr">
@@ -5028,7 +5040,11 @@
       </c>
       <c r="E6" s="66" t="n"/>
       <c r="F6" s="73" t="n"/>
-      <c r="G6" s="73" t="n"/>
+      <c r="G6" s="73" t="inlineStr">
+        <is>
+          <t>✅ Automated: test_vv_04_suspend_and_revoke. Passing on stage.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="85" t="inlineStr">
@@ -5056,7 +5072,11 @@
       </c>
       <c r="E7" s="66" t="n"/>
       <c r="F7" s="73" t="n"/>
-      <c r="G7" s="73" t="n"/>
+      <c r="G7" s="73" t="inlineStr">
+        <is>
+          <t>✅ Automated: test_vv_05_visit_tabs_render. Passing on stage.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="85" t="inlineStr">
@@ -5172,7 +5192,11 @@
       </c>
       <c r="E11" s="66" t="n"/>
       <c r="F11" s="73" t="n"/>
-      <c r="G11" s="73" t="n"/>
+      <c r="G11" s="73" t="inlineStr">
+        <is>
+          <t>✅ Automated: test_vv_09_visit_details_panel. Skips - blocked by user_visit_details 500 on covid_opp_test (opp missing OpportunityVerificationFlags config); product bug reported.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="85" t="inlineStr">
@@ -5848,7 +5872,7 @@
       <c r="F33" s="87" t="n"/>
       <c r="G33" s="73" t="inlineStr">
         <is>
-          <t>This test is for opp created before june 2</t>
+          <t>This test is for opp created before june 2 | ✅ Automated: test_vv_31_nm_reject_visit (NM org). Skips until a seeded manual-review opp with pending visits exists.</t>
         </is>
       </c>
     </row>
@@ -5879,7 +5903,7 @@
       <c r="F34" s="87" t="n"/>
       <c r="G34" s="73" t="inlineStr">
         <is>
-          <t>This test is for opp created before june 3</t>
+          <t>This test is for opp created before june 3 | ✅ Automated: test_vv_32_nm_approve_visit (NM org). Skips until a seeded manual-review opp with pending visits exists.</t>
         </is>
       </c>
     </row>
@@ -5910,7 +5934,7 @@
       <c r="F35" s="87" t="n"/>
       <c r="G35" s="73" t="inlineStr">
         <is>
-          <t>This test is for opp created before june 4</t>
+          <t>This test is for opp created before june 4 | ✅ Automated: test_vv_33_pm_agree_visit. Skips until seeded NM-approved / PM-review-pending visits exist.</t>
         </is>
       </c>
     </row>
@@ -5941,7 +5965,7 @@
       <c r="F36" s="87" t="n"/>
       <c r="G36" s="73" t="inlineStr">
         <is>
-          <t>This test is for opp created before june 5</t>
+          <t>This test is for opp created before june 5 | ✅ Automated: test_vv_34_pm_disagree_visit. Skips until seeded NM-approved / PM-review-pending visits exist.</t>
         </is>
       </c>
     </row>
@@ -6220,7 +6244,7 @@
       <c r="F47" s="73" t="inlineStr"/>
       <c r="G47" s="73" t="inlineStr">
         <is>
-          <t>Not automated (proposed, gap-derived). Priority: High. Action: Add to MTP + Automate (confirm w/ eng). Source: Gap Analysis GAP-SRC-W-40.</t>
+          <t>Partially covered by test_vv_05_visit_tabs_render (review tab-set renders); full mode x role matrix not yet automated.</t>
         </is>
       </c>
     </row>
@@ -6241,7 +6265,7 @@
       <c r="F48" s="73" t="inlineStr"/>
       <c r="G48" s="73" t="inlineStr">
         <is>
-          <t>Not automated (proposed, gap-derived). Priority: High. Action: Add to MTP + Automate (confirm w/ eng). Source: Gap Analysis GAP-SRC-W-41.</t>
+          <t>✅ Automated: test_gap_w_41_visit_table_waffle_mode_consistent. Passing on stage.</t>
         </is>
       </c>
     </row>
@@ -6262,7 +6286,7 @@
       <c r="F49" s="73" t="inlineStr"/>
       <c r="G49" s="73" t="inlineStr">
         <is>
-          <t>Not automated (proposed, gap-derived). Priority: High. Action: Add to MTP + Automate (confirm w/ eng). Source: Gap Analysis GAP-SRC-W-42.</t>
+          <t>Partially exercised by test_vv_01_land_and_bulk_approve (in-UI bulk Approve All); the 100-visit limit + justification rules not yet automated.</t>
         </is>
       </c>
     </row>
@@ -6283,7 +6307,7 @@
       <c r="F50" s="73" t="inlineStr"/>
       <c r="G50" s="73" t="inlineStr">
         <is>
-          <t>Not automated (proposed, gap-derived). Priority: High. Action: Add to MTP + Automate (confirm w/ eng). Source: Gap Analysis GAP-SRC-W-43.</t>
+          <t>✅ Automated: test_gap_w_43_bulk_controls_hidden_for_pm (passing). NM positive control test_gap_w_43_bulk_controls_visible_for_nm skips until a seeded manual-review opp.</t>
         </is>
       </c>
     </row>
@@ -6304,7 +6328,7 @@
       <c r="F51" s="73" t="inlineStr"/>
       <c r="G51" s="73" t="inlineStr">
         <is>
-          <t>Not automated (proposed, gap-derived). Priority: High. Action: Add to MTP + Automate (confirm w/ eng). Source: Gap Analysis GAP-SRC-W-44.</t>
+          <t>✅ Automated: test_gap_w_44_visit_action_bar_gating. Skips - blocked by user_visit_details 500 on covid_opp_test.</t>
         </is>
       </c>
     </row>
@@ -6325,7 +6349,7 @@
       <c r="F52" s="73" t="inlineStr"/>
       <c r="G52" s="73" t="inlineStr">
         <is>
-          <t>Not automated (proposed, gap-derived). Priority: Medium. Action: Add to MTP + Automate (confirm w/ eng). Source: Gap Analysis GAP-SRC-W-45.</t>
+          <t>✅ Automated: test_gap_w_45_manual_endpoint_403_under_auto_verify. Skips - blocked by user_visit_details 500; needs an auto-verify opp whose details render.</t>
         </is>
       </c>
     </row>

--- a/test_plans/CCC_Web_Platform_MTP.xlsx
+++ b/test_plans/CCC_Web_Platform_MTP.xlsx
@@ -5006,7 +5006,7 @@
       <c r="F5" s="73" t="n"/>
       <c r="G5" s="73" t="inlineStr">
         <is>
-          <t>✅ Automated: test_vv_03_image_carousel. Skips on covid_opp_test - blocked by user_visit_details 500 (opp missing OpportunityVerificationFlags); needs an opp whose details panel renders.</t>
+          <t>✅ Automated: test_vv_03_image_carousel. Skips when no scanned visit has a photo attachment - point WORKER_VISIT_VERIFICATION_PAGE_3 at a with-image visit to exercise it.</t>
         </is>
       </c>
     </row>
@@ -5194,7 +5194,7 @@
       <c r="F11" s="73" t="n"/>
       <c r="G11" s="73" t="inlineStr">
         <is>
-          <t>✅ Automated: test_vv_09_visit_details_panel. Skips - blocked by user_visit_details 500 on covid_opp_test (opp missing OpportunityVerificationFlags config); product bug reported.</t>
+          <t>✅ Automated: test_vv_09_visit_details_panel. Passing on stage.</t>
         </is>
       </c>
     </row>
@@ -6328,7 +6328,7 @@
       <c r="F51" s="73" t="inlineStr"/>
       <c r="G51" s="73" t="inlineStr">
         <is>
-          <t>✅ Automated: test_gap_w_44_visit_action_bar_gating. Skips - blocked by user_visit_details 500 on covid_opp_test.</t>
+          <t>✅ Automated: test_gap_w_44_visit_action_bar_gating. Passing on stage.</t>
         </is>
       </c>
     </row>
@@ -6349,7 +6349,7 @@
       <c r="F52" s="73" t="inlineStr"/>
       <c r="G52" s="73" t="inlineStr">
         <is>
-          <t>✅ Automated: test_gap_w_45_manual_endpoint_403_under_auto_verify. Skips - blocked by user_visit_details 500; needs an auto-verify opp whose details render.</t>
+          <t>✅ Automated: test_gap_w_45_manual_endpoint_403_under_auto_verify. Skips on covid_opp_test (it is manual-review, not auto-verify) - needs an auto-verify opp to run the 403 assertion.</t>
         </is>
       </c>
     </row>

--- a/test_plans/CCC_Web_Platform_MTP.xlsx
+++ b/test_plans/CCC_Web_Platform_MTP.xlsx
@@ -5986,7 +5986,7 @@
       <c r="F37" s="87" t="n"/>
       <c r="G37" s="73" t="inlineStr">
         <is>
-          <t>This test is for opp created before june 6</t>
+          <t>✅ Automated: test_vv_35_agree_and_disagree_are_mutually_exclusive (disagreed visit can't be agreed &amp; vice-versa). Skips until manual-review opp seeded.</t>
         </is>
       </c>
     </row>
@@ -6244,7 +6244,7 @@
       <c r="F47" s="73" t="inlineStr"/>
       <c r="G47" s="73" t="inlineStr">
         <is>
-          <t>Partially covered by test_vv_05_visit_tabs_render (review tab-set renders); full mode x role matrix not yet automated.</t>
+          <t>✅ Automated: test_gap_w_40_verification_tab_set_by_mode_and_role. Asserts PM sees Pending PM Review (not Pending NM Review), NM sees both, set ends with 'All'. Skips until manual-review opp seeded / when WORKER_VISITS_TASKS switch ON.</t>
         </is>
       </c>
     </row>
@@ -6286,7 +6286,7 @@
       <c r="F49" s="73" t="inlineStr"/>
       <c r="G49" s="73" t="inlineStr">
         <is>
-          <t>Partially exercised by test_vv_01_land_and_bulk_approve (in-UI bulk Approve All); the 100-visit limit + justification rules not yet automated.</t>
+          <t>✅ Automated (partial): test_gap_w_42_reject_requires_reason + test_gap_w_42_approve_requires_justification (mandatory reason/justification enforced). 100-visit bulk cap NOT covered (needs &gt;100 seeded visits).</t>
         </is>
       </c>
     </row>

--- a/test_plans/CCC_Web_Platform_MTP.xlsx
+++ b/test_plans/CCC_Web_Platform_MTP.xlsx
@@ -3645,7 +3645,7 @@
       <c r="F12" s="85" t="n"/>
       <c r="G12" s="88" t="inlineStr">
         <is>
-          <t>✅ Automated (Playwright): test_worker_lifecycle.py::test_connect_worker_09_resend_cooldown (real number +919000696488 -&gt; "sent in the last 24 hours"). NOTE: relies on the invite staying &lt;24h old; refresh if it flips.</t>
+          <t>🟡 Manual by design (decided 2026-10-02): the cooldown only exists for a real registered number and every invite/resend texts it, so it cannot be refreshed on each CI run without texting a real person (demo numbers send no SMS, so they never enforce the cooldown). test_worker_lifecycle.py::test_connect_worker_09_resend_cooldown (+919000696488, "sent in the last 24 hours") still verifies the refusal whenever the invite is &lt;24h old, e.g. right after a manual re-invite; otherwise it skips without resending. Run manually before releases.</t>
         </is>
       </c>
     </row>
@@ -32970,7 +32970,7 @@
       </c>
       <c r="D338" s="171" t="inlineStr">
         <is>
-          <t>🟢 Already automated</t>
+          <t>🟡 Manual by design</t>
         </is>
       </c>
       <c r="E338" s="171" t="inlineStr">
@@ -32985,7 +32985,7 @@
       </c>
       <c r="G338" s="171" t="inlineStr">
         <is>
-          <t>Already automated (n/a)</t>
+          <t>QA-owned (manual) - real-number cooldown; the test skips when the invite is &gt;24h old</t>
         </is>
       </c>
     </row>

--- a/test_plans/CCC_Web_Platform_MTP.xlsx
+++ b/test_plans/CCC_Web_Platform_MTP.xlsx
@@ -24978,12 +24978,12 @@
       </c>
       <c r="D122" s="171" t="inlineStr">
         <is>
-          <t>🔴 Manual only</t>
+          <t>🔴 Manual only (by design)</t>
         </is>
       </c>
       <c r="E122" s="171" t="inlineStr">
         <is>
-          <t>24-hr cooldown - time-dependent</t>
+          <t>Superseded: an automated test exists (Connect_worker_09, test_worker_lifecycle.py::test_connect_worker_09_resend_cooldown) but is manual by design - the cooldown needs a real registered number and every invite/resend texts it, so the invite cannot be refreshed on each CI run</t>
         </is>
       </c>
       <c r="F122" s="171" t="inlineStr">
@@ -25015,12 +25015,12 @@
       </c>
       <c r="D123" s="171" t="inlineStr">
         <is>
-          <t>🔴 Manual only</t>
+          <t>🟢 Already automated</t>
         </is>
       </c>
       <c r="E123" s="171" t="inlineStr">
         <is>
-          <t>24-hr cooldown - time-dependent</t>
+          <t>Closed: automated as Connect_worker_10, test_worker_lifecycle.py::test_connect_worker_10_resend_allowed_for_pending (seeded data, Worker_Lifecycle_Automation, 2026-09-10)</t>
         </is>
       </c>
       <c r="F123" s="171" t="inlineStr">
@@ -25030,7 +25030,7 @@
       </c>
       <c r="G123" s="171" t="inlineStr">
         <is>
-          <t>QA-owned (manual)</t>
+          <t>Already automated (n/a)</t>
         </is>
       </c>
     </row>
@@ -32970,7 +32970,7 @@
       </c>
       <c r="D338" s="171" t="inlineStr">
         <is>
-          <t>🟡 Manual by design</t>
+          <t>🔴 Manual only (by design)</t>
         </is>
       </c>
       <c r="E338" s="171" t="inlineStr">

--- a/test_plans/CCC_Web_Platform_MTP.xlsx
+++ b/test_plans/CCC_Web_Platform_MTP.xlsx
@@ -3645,7 +3645,7 @@
       <c r="F12" s="85" t="n"/>
       <c r="G12" s="88" t="inlineStr">
         <is>
-          <t>🟡 Manual by design (decided 2026-10-02): the cooldown only exists for a real registered number and every invite/resend texts it, so it cannot be refreshed on each CI run without texting a real person (demo numbers send no SMS, so they never enforce the cooldown). test_worker_lifecycle.py::test_connect_worker_09_resend_cooldown (+919000696488, "sent in the last 24 hours") still verifies the refusal whenever the invite is &lt;24h old, e.g. right after a manual re-invite; otherwise it skips without resending. Run manually before releases.</t>
+          <t>🔴 Manual only (by design) (decided 2026-10-02): the cooldown only exists for a real registered number and every invite/resend texts it, so it cannot be refreshed on each CI run without texting a real person (demo numbers send no SMS, so they never enforce the cooldown). test_worker_lifecycle.py::test_connect_worker_09_resend_cooldown (+919000696488, "sent in the last 24 hours") still verifies the refusal whenever the invite is &lt;24h old, e.g. right after a manual re-invite; otherwise it skips without resending. Run manually before releases.</t>
         </is>
       </c>
     </row>

--- a/test_plans/CCC_Web_Platform_MTP.xlsx
+++ b/test_plans/CCC_Web_Platform_MTP.xlsx
@@ -3645,7 +3645,7 @@
       <c r="F12" s="85" t="n"/>
       <c r="G12" s="88" t="inlineStr">
         <is>
-          <t>🔴 Manual only (by design) (decided 2026-10-02): the cooldown only exists for a real registered number and every invite/resend texts it, so it cannot be refreshed on each CI run without texting a real person (demo numbers send no SMS, so they never enforce the cooldown). test_worker_lifecycle.py::test_connect_worker_09_resend_cooldown (+919000696488, "sent in the last 24 hours") still verifies the refusal whenever the invite is &lt;24h old, e.g. right after a manual re-invite; otherwise it skips without resending. Run manually before releases.</t>
+          <t>🔴 Manual only (by design) (decided 2026-10-02): the cooldown only exists for a real registered number and every invite/resend texts it, so it cannot be refreshed on each CI run without texting a real person (demo numbers send no SMS, so they never enforce the cooldown). No automated test; QA runs it by hand before releases.</t>
         </is>
       </c>
     </row>
@@ -24983,7 +24983,7 @@
       </c>
       <c r="E122" s="171" t="inlineStr">
         <is>
-          <t>Superseded: an automated test exists (Connect_worker_09, test_worker_lifecycle.py::test_connect_worker_09_resend_cooldown) but is manual by design - the cooldown needs a real registered number and every invite/resend texts it, so the invite cannot be refreshed on each CI run</t>
+          <t>Manual only (by design): the cooldown needs a real registered number and every invite/resend texts it, so there is no automated test.</t>
         </is>
       </c>
       <c r="F122" s="171" t="inlineStr">
@@ -32975,7 +32975,7 @@
       </c>
       <c r="E338" s="171" t="inlineStr">
         <is>
-          <t>test_worker_lifecycle.py::test_connect_worker_09_resend_cooldown</t>
+          <t>No automated test - manual by design (real-number cooldown)</t>
         </is>
       </c>
       <c r="F338" s="171" t="inlineStr">
@@ -32985,7 +32985,7 @@
       </c>
       <c r="G338" s="171" t="inlineStr">
         <is>
-          <t>QA-owned (manual) - real-number cooldown; the test skips when the invite is &gt;24h old</t>
+          <t>QA-owned (manual) - real-number cooldown; run by hand before releases</t>
         </is>
       </c>
     </row>

--- a/test_plans/CCC_Web_Platform_MTP.xlsx
+++ b/test_plans/CCC_Web_Platform_MTP.xlsx
@@ -5872,7 +5872,7 @@
       <c r="F33" s="87" t="n"/>
       <c r="G33" s="73" t="inlineStr">
         <is>
-          <t>This test is for opp created before june 2 | ✅ Automated: test_vv_31_nm_reject_visit (NM org). Skips until a seeded manual-review opp with pending visits exists.</t>
+          <t>This test is for opp created before june 2 | ✅ Automated: test_vv_31_nm_reject_visit (NM org). Runs on prod and staging against the seeded 'Manual approval opp'. The tests top up their own pool of visits by submitting the delivery form in HQ Web Apps as the worker ('Log in as'), so no manual reseeding.</t>
         </is>
       </c>
     </row>
@@ -5903,7 +5903,7 @@
       <c r="F34" s="87" t="n"/>
       <c r="G34" s="73" t="inlineStr">
         <is>
-          <t>This test is for opp created before june 3 | ✅ Automated: test_vv_32_nm_approve_visit (NM org). Skips until a seeded manual-review opp with pending visits exists.</t>
+          <t>This test is for opp created before june 3 | ✅ Automated: test_vv_32_nm_approve_visit (NM org). Runs on prod and staging against the seeded 'Manual approval opp'. The tests top up their own pool of visits by submitting the delivery form in HQ Web Apps as the worker ('Log in as'), so no manual reseeding.</t>
         </is>
       </c>
     </row>
@@ -5934,7 +5934,7 @@
       <c r="F35" s="87" t="n"/>
       <c r="G35" s="73" t="inlineStr">
         <is>
-          <t>This test is for opp created before june 4 | ✅ Automated: test_vv_33_pm_agree_visit. Skips until seeded NM-approved / PM-review-pending visits exist.</t>
+          <t>This test is for opp created before june 4 | ✅ Automated: test_vv_33_pm_agree_visit. Runs on prod and staging against the seeded 'Manual approval opp'. The tests top up their own pool of visits by submitting the delivery form in HQ Web Apps as the worker ('Log in as'), so no manual reseeding. PM-review-pending visits come from the fixture NM-approving fresh visits.</t>
         </is>
       </c>
     </row>
@@ -5965,7 +5965,7 @@
       <c r="F36" s="87" t="n"/>
       <c r="G36" s="73" t="inlineStr">
         <is>
-          <t>This test is for opp created before june 5 | ✅ Automated: test_vv_34_pm_disagree_visit. Skips until seeded NM-approved / PM-review-pending visits exist.</t>
+          <t>This test is for opp created before june 5 | ✅ Automated: test_vv_34_pm_disagree_visit. Runs on prod and staging against the seeded 'Manual approval opp'. The tests top up their own pool of visits by submitting the delivery form in HQ Web Apps as the worker ('Log in as'), so no manual reseeding. PM-review-pending visits come from the fixture NM-approving fresh visits.</t>
         </is>
       </c>
     </row>
@@ -5986,7 +5986,7 @@
       <c r="F37" s="87" t="n"/>
       <c r="G37" s="73" t="inlineStr">
         <is>
-          <t>✅ Automated: test_vv_35_agree_and_disagree_are_mutually_exclusive (disagreed visit can't be agreed &amp; vice-versa). Skips until manual-review opp seeded.</t>
+          <t>✅ Automated, split in two: test_vv_35_agree_then_cannot_disagree PASSES (after Agree, Disagree is disabled). test_vv_35_disagree_then_cannot_agree is an EXPECTED FAILURE (xfail): the product leaves Agree enabled after Disagree (Agree is only disabled once the visit is already agreed), so a PM can flip disagree -&gt; agree, which contradicts this case. Product bug or plan inaccuracy - decision pending (seen on prod and staging, 2026-10-16).</t>
         </is>
       </c>
     </row>
@@ -6244,7 +6244,7 @@
       <c r="F47" s="73" t="inlineStr"/>
       <c r="G47" s="73" t="inlineStr">
         <is>
-          <t>✅ Automated: test_gap_w_40_verification_tab_set_by_mode_and_role. Asserts PM sees Pending PM Review (not Pending NM Review), NM sees both, set ends with 'All'. Skips until manual-review opp seeded / when WORKER_VISITS_TASKS switch ON.</t>
+          <t>✅ Automated: test_gap_w_40_verification_tab_set_by_mode_and_role. Asserts PM sees Pending PM Review (not Pending NM Review), NM sees both, set ends with 'All'. Currently SKIPS on prod and staging: the seeded manual-review opps have the WORKER_VISITS_TASKS switch ON (plain Visits/Tasks table, no NM-review tab-set); needs an opp with the switch OFF.</t>
         </is>
       </c>
     </row>
@@ -6286,7 +6286,7 @@
       <c r="F49" s="73" t="inlineStr"/>
       <c r="G49" s="73" t="inlineStr">
         <is>
-          <t>✅ Automated (partial): test_gap_w_42_reject_requires_reason + test_gap_w_42_approve_requires_justification (mandatory reason/justification enforced). 100-visit bulk cap NOT covered (needs &gt;100 seeded visits).</t>
+          <t>✅ Automated (partial): test_gap_w_42_reject_requires_reason + test_gap_w_42_approve_requires_justification - both passing on prod and staging (the reject textarea has no 'required' attribute, but the server refuses an empty reason; approve's justification is required client-side). 100-visit bulk cap NOT covered (needs &gt;100 seeded visits).</t>
         </is>
       </c>
     </row>
@@ -6307,7 +6307,7 @@
       <c r="F50" s="73" t="inlineStr"/>
       <c r="G50" s="73" t="inlineStr">
         <is>
-          <t>✅ Automated: test_gap_w_43_bulk_controls_hidden_for_pm (passing). NM positive control test_gap_w_43_bulk_controls_visible_for_nm skips until a seeded manual-review opp.</t>
+          <t>✅ Automated: test_gap_w_43_bulk_controls_hidden_for_pm (passing). NM positive control test_gap_w_43_bulk_controls_visible_for_nm SKIPS: bulk controls belong to the tabbed verification table, which is absent when the WORKER_VISITS_TASKS switch is ON (the case on the seeded opps).</t>
         </is>
       </c>
     </row>
